--- a/docs/downloads/经营分_山西省区__山西北片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_山西省区__山西北片区_2026-10-18.xlsx
@@ -1131,17 +1131,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>7081220555378001960</t>
+          <t>7494467627922753555</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7天优品（大同第五人民医院店）</t>
+          <t>锦江之星(大同古城华严寺酒店)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7天优品酒店(大同第五人民医院店)</t>
+          <t>锦江之星(大同古城武定门酒店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1150,36 +1150,36 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
         <v>10</v>
       </c>
       <c r="M7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" t="n">
+        <v>30</v>
+      </c>
+      <c r="O7" t="n">
         <v>25</v>
       </c>
-      <c r="N7" t="n">
-        <v>30</v>
-      </c>
-      <c r="O7" t="n">
-        <v>20</v>
-      </c>
       <c r="P7" t="n">
         <v>30</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R7" t="n">
         <v>30</v>
@@ -1219,17 +1219,17 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6785296357017126923</t>
+          <t>7081220555378001960</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>锦江之星品尚(大同火车站酒店)</t>
+          <t>7天优品（大同第五人民医院店）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>锦江之星品尚(大同火车站店)</t>
+          <t>7天优品酒店(大同第五人民医院店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1238,24 +1238,24 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N8" t="n">
         <v>30</v>
@@ -1307,17 +1307,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7626244734908860451</t>
+          <t>6785296357017126923</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>麗枫酒店（浑源古城悬空寺店）</t>
+          <t>锦江之星品尚(大同火车站酒店)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>麗枫酒店(浑源古城悬空寺店)</t>
+          <t>锦江之星品尚(大同火车站店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="N9" t="n">
         <v>30</v>
@@ -1355,7 +1355,7 @@
         <v>30</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R9" t="n">
         <v>30</v>
@@ -1395,29 +1395,29 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>7035911118157514784</t>
+          <t>7626244734908860451</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7天优品Premium（市政府大同大学店）</t>
+          <t>麗枫酒店（浑源古城悬空寺店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7天优品Premium(市政府大同大学店)</t>
+          <t>麗枫酒店(浑源古城悬空寺店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I10" t="n">
-        <v>-5</v>
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1431,19 +1431,19 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
+        <v>14</v>
+      </c>
+      <c r="N10" t="n">
+        <v>30</v>
+      </c>
+      <c r="O10" t="n">
+        <v>20</v>
+      </c>
+      <c r="P10" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q10" t="n">
         <v>25</v>
-      </c>
-      <c r="N10" t="n">
-        <v>30</v>
-      </c>
-      <c r="O10" t="n">
-        <v>25</v>
-      </c>
-      <c r="P10" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>10</v>
       </c>
       <c r="R10" t="n">
         <v>30</v>
@@ -1747,29 +1747,29 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7494467627922753555</t>
+          <t>6601148840277968909</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>锦江之星(大同古城华严寺酒店)</t>
+          <t>锦江之星(大同古城平城桥店)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>锦江之星(大同古城武定门酒店)</t>
+          <t>锦江之星酒店(平城桥店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>90</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1783,19 +1783,19 @@
         <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N14" t="n">
         <v>30</v>
       </c>
       <c r="O14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P14" t="n">
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -1835,17 +1835,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>6601148840277968909</t>
+          <t>7035911118157514784</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>锦江之星(大同古城平城桥店)</t>
+          <t>7天优品Premium（市政府大同大学店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>锦江之星酒店(平城桥店)</t>
+          <t>7天优品Premium(市政府大同大学店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1871,19 +1871,19 @@
         <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N15" t="n">
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
@@ -1923,33 +1923,33 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>6919967936090228750</t>
+          <t>6857513639226640384</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（大同古城华严寺店）</t>
+          <t>维也纳酒店（大同高铁站东信国际店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(大同古城店)</t>
+          <t>维也纳酒店(大同高铁站东信国际店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>95</v>
       </c>
       <c r="I16" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1959,7 +1959,7 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N16" t="n">
         <v>30</v>
@@ -1971,7 +1971,7 @@
         <v>30</v>
       </c>
       <c r="Q16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R16" t="n">
         <v>30</v>
@@ -2011,29 +2011,29 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>6601148990631184397</t>
+          <t>7389086049038764067</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>维也纳酒店（大同高铁站万达广场店）</t>
+          <t>锦江之星（大同古城迎宾街酒店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>维也纳酒店(山西大同高铁站万达广场店)</t>
+          <t>锦江之星(大同古城迎宾街酒店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>95</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2053,13 +2053,13 @@
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P17" t="n">
         <v>30</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R17" t="n">
         <v>30</v>
@@ -2099,33 +2099,33 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>6857513639226640384</t>
+          <t>7368725720052271167</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>维也纳酒店（大同高铁站东信国际店）</t>
+          <t>丽怡酒店（大同古城店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>维也纳酒店(大同高铁站东信国际店)</t>
+          <t>丽怡酒店(大同古城店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2135,19 +2135,19 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N18" t="n">
         <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P18" t="n">
         <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2182,22 +2182,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>忻州市</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7389086049038764067</t>
+          <t>6601140766808999949</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>锦江之星（大同古城迎宾街酒店）</t>
+          <t>喆啡酒店（忻州古城开来欣悦购物广场店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>锦江之星(大同古城迎宾街酒店)</t>
+          <t>喆啡酒店(忻州和平路店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2206,14 +2206,14 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2223,19 +2223,19 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
       </c>
       <c r="O19" t="n">
+        <v>20</v>
+      </c>
+      <c r="P19" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q19" t="n">
         <v>25</v>
-      </c>
-      <c r="P19" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>10</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2275,17 +2275,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7368725720052271167</t>
+          <t>7077026661430757414</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>丽怡酒店（大同古城店）</t>
+          <t>麗枫酒店(大同高铁站方特店)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>丽怡酒店(大同古城店)</t>
+          <t>麗枫酒店(大同高铁站方特店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2297,7 +2297,7 @@
         <v>97</v>
       </c>
       <c r="I20" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
@@ -2323,7 +2323,7 @@
         <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R20" t="n">
         <v>30</v>
@@ -2358,22 +2358,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>忻州市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>6601140766808999949</t>
+          <t>6601148538246154244</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>喆啡酒店（忻州古城开来欣悦购物广场店）</t>
+          <t>7天酒店（大同火车站店）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>喆啡酒店(忻州和平路店)</t>
+          <t>7天酒店(大同火车站店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2399,19 +2399,19 @@
         <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
         <v>30</v>
       </c>
       <c r="O21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P21" t="n">
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
@@ -2451,17 +2451,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>7077026661430757414</t>
+          <t>7501791705801164815</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>麗枫酒店(大同高铁站方特店)</t>
+          <t>喆啡酒店（大同古城华严寺店）</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>麗枫酒店(大同高铁站方特店)</t>
+          <t>喆啡酒店(大同古城华严寺店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2470,14 +2470,14 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -2487,19 +2487,19 @@
         <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N22" t="n">
         <v>30</v>
       </c>
       <c r="O22" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
         <v>30</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R22" t="n">
         <v>30</v>
@@ -2534,22 +2534,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>忻州市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>6601142784051120131</t>
+          <t>7662262592013862963</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7天酒店(忻州古城市政府店)</t>
+          <t>大同南站万达广场丽柏酒店</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>7天酒店(忻州古城市政府店)</t>
+          <t>大同南站万达广场丽柏酒店</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2561,11 +2561,11 @@
         <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -2575,13 +2575,13 @@
         <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N23" t="n">
         <v>30</v>
       </c>
       <c r="O23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P23" t="n">
         <v>30</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>6601148538246154244</t>
+          <t>7401777865106130985</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7天酒店（大同火车站店）</t>
+          <t>大同古城丽柏酒店</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7天酒店(大同火车站店)</t>
+          <t>大同古城丽柏酒店</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2663,7 +2663,7 @@
         <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N24" t="n">
         <v>30</v>
@@ -2675,7 +2675,7 @@
         <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R24" t="n">
         <v>30</v>
@@ -2715,17 +2715,17 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>7501791705801164815</t>
+          <t>6919967936090228750</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>喆啡酒店（大同古城华严寺店）</t>
+          <t>维也纳3好酒店（大同古城华严寺店）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>喆啡酒店(大同古城华严寺店)</t>
+          <t>维也纳3好酒店(大同古城店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2737,7 +2737,7 @@
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2757,13 +2757,13 @@
         <v>30</v>
       </c>
       <c r="O25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P25" t="n">
         <v>30</v>
       </c>
       <c r="Q25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R25" t="n">
         <v>30</v>
@@ -2803,29 +2803,29 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>7662262592013862963</t>
+          <t>7264177468758558760</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>大同南站万达广场丽柏酒店</t>
+          <t>维也纳国际酒店(大同古城火车站店)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>大同南站万达广场丽柏酒店</t>
+          <t>维也纳国际酒店(大同古城火车站店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2845,13 +2845,13 @@
         <v>30</v>
       </c>
       <c r="O26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P26" t="n">
         <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R26" t="n">
         <v>30</v>
@@ -2891,17 +2891,17 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>7401777865106130985</t>
+          <t>6601148990631184397</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>大同古城丽柏酒店</t>
+          <t>维也纳酒店（大同高铁站万达广场店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>大同古城丽柏酒店</t>
+          <t>维也纳酒店(山西大同高铁站万达广场店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2913,7 +2913,7 @@
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2979,29 +2979,29 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7264177468758558760</t>
+          <t>6601264614195873800</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(大同古城火车站店)</t>
+          <t>麗枫酒店(大同东信广场高铁站店)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(大同古城火车站店)</t>
+          <t>丽枫酒店(大同东信广场高铁站店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -3067,17 +3067,17 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>6601264614195873800</t>
+          <t>7635900194107230248</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>麗枫酒店(大同东信广场高铁站店)</t>
+          <t>麗枫酒店(大同古城华严寺店)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>丽枫酒店(大同东信广场高铁站店)</t>
+          <t>麗枫酒店(大同古城华严寺店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -3103,7 +3103,7 @@
         <v>10</v>
       </c>
       <c r="M29" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N29" t="n">
         <v>30</v>
@@ -3115,7 +3115,7 @@
         <v>30</v>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="R29" t="n">
         <v>30</v>
@@ -3150,38 +3150,38 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>忻州市</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7635900194107230248</t>
+          <t>7278641696152242188</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>麗枫酒店(大同古城华严寺店)</t>
+          <t>IU酒店（忻州古城居然之家店）</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>麗枫酒店(大同古城华严寺店)</t>
+          <t>iu酒店(忻州居然之家店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I30" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>稳房源,提质量</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -3191,7 +3191,7 @@
         <v>10</v>
       </c>
       <c r="M30" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="N30" t="n">
         <v>30</v>
@@ -3203,7 +3203,7 @@
         <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="R30" t="n">
         <v>30</v>
@@ -3243,17 +3243,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>7278641696152242188</t>
+          <t>6679148759789602823</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IU酒店（忻州古城居然之家店）</t>
+          <t>IU酒店（忻州古城高铁西站店）</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>iu酒店(忻州居然之家店)</t>
+          <t>IU酒店(忻州古城高铁西站店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -3279,13 +3279,13 @@
         <v>10</v>
       </c>
       <c r="M31" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N31" t="n">
         <v>30</v>
       </c>
       <c r="O31" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P31" t="n">
         <v>30</v>
@@ -3331,17 +3331,17 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>6679148759789602823</t>
+          <t>6993637003162028039</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IU酒店（忻州古城高铁西站店）</t>
+          <t>麗枫酒店(忻州古城店)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>IU酒店(忻州古城高铁西站店)</t>
+          <t>麗枫酒店(忻州古城店)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -3367,13 +3367,13 @@
         <v>10</v>
       </c>
       <c r="M32" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N32" t="n">
         <v>30</v>
       </c>
       <c r="O32" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P32" t="n">
         <v>30</v>
@@ -3419,22 +3419,22 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>6993637003162028039</t>
+          <t>7471067360556746763</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>麗枫酒店(忻州古城店)</t>
+          <t>麗枫酒店(忻州开来欣悦购物广场旗舰店)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>麗枫酒店(忻州古城店)</t>
+          <t>麗枫酒店(忻州开莱欣悦购物广场旗舰店)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -3461,13 +3461,13 @@
         <v>30</v>
       </c>
       <c r="O33" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P33" t="n">
         <v>30</v>
       </c>
       <c r="Q33" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R33" t="n">
         <v>30</v>
@@ -3507,33 +3507,33 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>7471067360556746763</t>
+          <t>6601142784051120131</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>麗枫酒店(忻州开来欣悦购物广场旗舰店)</t>
+          <t>7天酒店(忻州古城市政府店)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>麗枫酒店(忻州开莱欣悦购物广场旗舰店)</t>
+          <t>7天酒店(忻州古城市政府店)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -3543,13 +3543,13 @@
         <v>10</v>
       </c>
       <c r="M34" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N34" t="n">
         <v>30</v>
       </c>
       <c r="O34" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P34" t="n">
         <v>30</v>
@@ -3705,7 +3705,7 @@
         <v>105</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -4123,17 +4123,17 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>7417336175620278291</t>
+          <t>7436249058991147019</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>锦江之星（大同南站东信万达广场店）</t>
+          <t>锦江之星（大同恒山悬空寺浑源古城酒店）</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>锦江之星酒店(大同南站东信广场店)</t>
+          <t>锦江之星(大同恒山悬空寺浑源古城酒店)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4145,11 +4145,11 @@
         <v>105</v>
       </c>
       <c r="I41" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -4165,13 +4165,13 @@
         <v>30</v>
       </c>
       <c r="O41" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P41" t="n">
         <v>30</v>
       </c>
       <c r="Q41" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R41" t="n">
         <v>30</v>
@@ -4211,17 +4211,17 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>7436249058991147019</t>
+          <t>7477087231224580148</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>锦江之星（大同恒山悬空寺浑源古城酒店）</t>
+          <t>非繁云居酒店（大同古城华严寺店）</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>锦江之星(大同恒山悬空寺浑源古城酒店)</t>
+          <t>云居酒店(大同古城华严寺店)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -4247,19 +4247,19 @@
         <v>10</v>
       </c>
       <c r="M42" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N42" t="n">
         <v>30</v>
       </c>
       <c r="O42" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P42" t="n">
         <v>30</v>
       </c>
       <c r="Q42" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R42" t="n">
         <v>30</v>
@@ -4299,17 +4299,17 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>7477087231224580148</t>
+          <t>7505410903254829071</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>非繁云居酒店（大同古城华严寺店）</t>
+          <t>凯里亚德酒店（大同古城大润发店）</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>云居酒店(大同古城华严寺店)</t>
+          <t>凯里亚德酒店(大同西环路大润发店)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>30</v>
       </c>
       <c r="Q43" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R43" t="n">
         <v>30</v>
@@ -4382,38 +4382,38 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>朔州市</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>7505410903254829071</t>
+          <t>7255874167298328628</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>凯里亚德酒店（大同古城大润发店）</t>
+          <t>潮漫酒店(朔州应县木塔店)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(大同西环路大润发店)</t>
+          <t>潮漫酒店(朔州应县木塔店)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H44" t="n">
         <v>110</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -4429,13 +4429,13 @@
         <v>30</v>
       </c>
       <c r="O44" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P44" t="n">
         <v>30</v>
       </c>
       <c r="Q44" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R44" t="n">
         <v>30</v>
@@ -4470,27 +4470,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>朔州市</t>
+          <t>忻州市</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>7255874167298328628</t>
+          <t>7119712870631213088</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>潮漫酒店(朔州应县木塔店)</t>
+          <t>维也纳3好酒店（五台山店）</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>潮漫酒店(朔州应县木塔店)</t>
+          <t>维也纳3好酒店(五台山店)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -4517,13 +4517,13 @@
         <v>30</v>
       </c>
       <c r="O45" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P45" t="n">
         <v>30</v>
       </c>
       <c r="Q45" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R45" t="n">
         <v>30</v>
@@ -4558,27 +4558,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>忻州市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>7119712870631213088</t>
+          <t>7417336175620278291</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（五台山店）</t>
+          <t>锦江之星（大同南站东信万达广场店）</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(五台山店)</t>
+          <t>锦江之星酒店(大同南站东信广场店)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -4599,7 +4599,7 @@
         <v>10</v>
       </c>
       <c r="M46" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N46" t="n">
         <v>30</v>
@@ -4611,7 +4611,7 @@
         <v>30</v>
       </c>
       <c r="Q46" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R46" t="n">
         <v>30</v>
